--- a/data/trans_dic/P43E-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P43E-Provincia-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,8; 30,81</t>
+          <t>18,47; 31,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,35; 31,97</t>
+          <t>18,73; 30,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 19,96</t>
+          <t>10,99; 18,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,8; 30,81</t>
+          <t>18,47; 31,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,35; 31,97</t>
+          <t>18,73; 30,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 19,96</t>
+          <t>10,99; 18,9</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 26,13</t>
+          <t>16,96; 26,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 18,72</t>
+          <t>11,27; 18,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,51; 31,57</t>
+          <t>21,09; 30,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 26,13</t>
+          <t>16,96; 26,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 18,72</t>
+          <t>11,27; 18,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,51; 31,57</t>
+          <t>21,09; 30,74</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 32,53</t>
+          <t>18,81; 32,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,71</t>
+          <t>2,6; 8,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,87; 22,68</t>
+          <t>12,74; 22,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 32,53</t>
+          <t>18,81; 32,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,71</t>
+          <t>2,6; 8,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,87; 22,68</t>
+          <t>12,74; 22,31</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,73; 32,27</t>
+          <t>21,23; 32,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 16,6</t>
+          <t>7,44; 16,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 20,46</t>
+          <t>16,27; 25,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,73; 32,27</t>
+          <t>21,23; 32,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 16,6</t>
+          <t>7,44; 16,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 20,46</t>
+          <t>16,27; 25,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,45; 29,93</t>
+          <t>15,39; 30,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 19,42</t>
+          <t>6,3; 19,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,24; 33,06</t>
+          <t>19,8; 33,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,45; 29,93</t>
+          <t>15,39; 30,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 19,42</t>
+          <t>6,3; 19,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,24; 33,06</t>
+          <t>19,8; 33,87</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,7; 27,43</t>
+          <t>12,39; 26,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,04; 37,54</t>
+          <t>16,01; 37,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,58; 25,42</t>
+          <t>12,89; 25,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,7; 27,43</t>
+          <t>12,39; 26,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,04; 37,54</t>
+          <t>16,01; 37,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,58; 25,42</t>
+          <t>12,89; 25,51</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,57; 28,61</t>
+          <t>20,19; 29,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,64; 26,39</t>
+          <t>17,92; 26,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,27; 47,43</t>
+          <t>36,91; 46,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,57; 28,61</t>
+          <t>20,19; 29,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,64; 26,39</t>
+          <t>17,92; 26,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,27; 47,43</t>
+          <t>36,91; 46,23</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1195,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,1; 25,33</t>
+          <t>17,84; 25,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,9; 21,49</t>
+          <t>14,26; 21,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,67; 17,61</t>
+          <t>10,73; 18,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,1; 25,33</t>
+          <t>17,84; 25,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,9; 21,49</t>
+          <t>14,26; 21,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,67; 17,61</t>
+          <t>10,73; 18,06</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -1275,32 +1275,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21,08; 24,84</t>
+          <t>21,27; 24,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,83; 17,99</t>
+          <t>14,8; 18,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,17; 25,19</t>
+          <t>22,7; 26,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,08; 24,84</t>
+          <t>21,27; 24,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,83; 17,99</t>
+          <t>14,8; 18,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,17; 25,19</t>
+          <t>22,7; 26,4</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>26770</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35550; 61538</t>
+          <t>36901; 63246</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38641; 63833</t>
+          <t>37392; 61563</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19390; 33727</t>
+          <t>20060; 34485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35550; 61538</t>
+          <t>36901; 63246</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38641; 63833</t>
+          <t>37392; 61563</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19390; 33727</t>
+          <t>20060; 34485</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>62178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>62178</t>
         </is>
       </c>
     </row>
@@ -1622,32 +1622,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64016; 96688</t>
+          <t>62734; 97189</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42906; 71121</t>
+          <t>42824; 70274</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50078; 73485</t>
+          <t>50993; 74312</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64016; 96688</t>
+          <t>62734; 97189</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42906; 71121</t>
+          <t>42824; 70274</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50078; 73485</t>
+          <t>50993; 74312</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>27805</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>27805</t>
         </is>
       </c>
     </row>
@@ -1740,32 +1740,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35569; 61664</t>
+          <t>35643; 60687</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6418; 21610</t>
+          <t>6440; 21924</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20035; 35323</t>
+          <t>20449; 35815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35569; 61664</t>
+          <t>35643; 60687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6418; 21610</t>
+          <t>6440; 21924</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20035; 35323</t>
+          <t>20449; 35815</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38137</t>
+          <t>42993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38137</t>
+          <t>42993</t>
         </is>
       </c>
     </row>
@@ -1858,32 +1858,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52366; 81514</t>
+          <t>53642; 82247</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21445; 44031</t>
+          <t>19734; 43161</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18723; 59360</t>
+          <t>34113; 53749</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52366; 81514</t>
+          <t>53642; 82247</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21445; 44031</t>
+          <t>19734; 43161</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18723; 59360</t>
+          <t>34113; 53749</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>16790</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21112; 40902</t>
+          <t>21036; 41535</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5358; 16420</t>
+          <t>5327; 16306</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11419; 19619</t>
+          <t>12784; 21869</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21112; 40902</t>
+          <t>21036; 41535</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5358; 16420</t>
+          <t>5327; 16306</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11419; 19619</t>
+          <t>12784; 21869</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15762</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15762</t>
+          <t>16349</t>
         </is>
       </c>
     </row>
@@ -2094,32 +2094,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19121; 41309</t>
+          <t>18661; 40235</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9913; 23198</t>
+          <t>9891; 23182</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10835; 21890</t>
+          <t>11465; 22681</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19121; 41309</t>
+          <t>18661; 40235</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9913; 23198</t>
+          <t>9891; 23182</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10835; 21890</t>
+          <t>11465; 22681</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>143821</t>
+          <t>164307</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>143821</t>
+          <t>164307</t>
         </is>
       </c>
     </row>
@@ -2212,32 +2212,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>84357; 123293</t>
+          <t>87027; 125591</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>76632; 108466</t>
+          <t>73639; 107858</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>128940; 159780</t>
+          <t>145451; 182214</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84357; 123293</t>
+          <t>87027; 125591</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>76632; 108466</t>
+          <t>73639; 107858</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>128940; 159780</t>
+          <t>145451; 182214</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>38013</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>38013</t>
         </is>
       </c>
     </row>
@@ -2330,32 +2330,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>93935; 131431</t>
+          <t>92577; 131341</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>69936; 108169</t>
+          <t>71780; 108606</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25705; 42413</t>
+          <t>28699; 48310</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>93935; 131431</t>
+          <t>92577; 131341</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>69936; 108169</t>
+          <t>71780; 108606</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25705; 42413</t>
+          <t>28699; 48310</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
     </row>
@@ -2448,32 +2448,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>474104; 558644</t>
+          <t>478474; 559306</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>319342; 387366</t>
+          <t>318740; 387912</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>301053; 395733</t>
+          <t>365309; 424889</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>474104; 558644</t>
+          <t>478474; 559306</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>319342; 387366</t>
+          <t>318740; 387912</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>301053; 395733</t>
+          <t>365309; 424889</t>
         </is>
       </c>
     </row>
